--- a/data/SOM_SSD_KEN_SUB_INDICATOR_MASTER.xlsx
+++ b/data/SOM_SSD_KEN_SUB_INDICATOR_MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Documents\GitHub\Socioeconomic-Peace-Index-Tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B1B43A-E20E-4FE1-9039-F877EC9CA1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266812FC-CE34-45A0-A38D-5827C24D5E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3AC3E778-01FB-4C22-AA56-BA37C4D01EF8}"/>
+    <workbookView xWindow="3795" yWindow="3795" windowWidth="21600" windowHeight="11205" activeTab="2" xr2:uid="{3AC3E778-01FB-4C22-AA56-BA37C4D01EF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Kenya" sheetId="1" r:id="rId1"/>
@@ -4579,49 +4579,49 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2">
-        <v>0.66037735799999997</v>
+        <v>0.30188679200000001</v>
       </c>
       <c r="E2" s="2">
-        <v>0.61428571399999998</v>
+        <v>0.492857143</v>
       </c>
       <c r="F2" s="2">
-        <v>0.14592639900000001</v>
+        <v>0.95288236500000001</v>
       </c>
       <c r="G2" s="2">
-        <v>0.58025802599999998</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>0.516404643</v>
+        <v>0.35188138699999999</v>
       </c>
       <c r="I2" s="2">
-        <v>0.34610756100000001</v>
+        <v>0.61653771800000001</v>
       </c>
       <c r="J2" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2">
-        <v>0.562139053</v>
+        <v>0.12986002599999999</v>
       </c>
       <c r="L2" s="2">
-        <v>8.8109093999999999E-2</v>
+        <v>0.60092788799999997</v>
       </c>
       <c r="M2" s="2">
-        <v>0.59576597600000003</v>
+        <v>5.1697329E-2</v>
       </c>
       <c r="N2" s="2">
-        <v>0.28821811400000003</v>
+        <v>0.67434201100000002</v>
       </c>
       <c r="O2" s="2">
-        <v>0.26039265900000003</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2">
-        <v>0.312149079</v>
+        <v>0.49508760099999999</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -4635,49 +4635,49 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2">
-        <v>0.75471698099999995</v>
+        <v>0.96855345900000001</v>
       </c>
       <c r="E3" s="2">
-        <v>0.62142857100000004</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>0.31078493899999998</v>
       </c>
       <c r="G3" s="2">
-        <v>0.56295629599999997</v>
+        <v>0.62266226599999996</v>
       </c>
       <c r="H3" s="2">
-        <v>0.146887608</v>
+        <v>9.5431956999999998E-2</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6667902999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K3" s="2">
-        <v>0.27595732299999998</v>
+        <v>0.531891687</v>
       </c>
       <c r="L3" s="2">
-        <v>0.21956430399999999</v>
+        <v>0.144734372</v>
       </c>
       <c r="M3" s="2">
-        <v>0.56511400899999997</v>
+        <v>0.20195196300000001</v>
       </c>
       <c r="N3" s="2">
-        <v>0.27506281599999999</v>
+        <v>0.79734716800000005</v>
       </c>
       <c r="O3" s="2">
-        <v>0.68108515999999997</v>
+        <v>0.192511933</v>
       </c>
       <c r="P3" s="2">
-        <v>0.65638742400000005</v>
+        <v>0.491921049</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -4691,49 +4691,49 @@
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2">
-        <v>0.77358490599999996</v>
+        <v>0.94339622599999995</v>
       </c>
       <c r="E4" s="2">
-        <v>0.571428571</v>
+        <v>0.2</v>
       </c>
       <c r="F4" s="2">
-        <v>0.41289087400000002</v>
+        <v>0.31652839799999999</v>
       </c>
       <c r="G4" s="2">
-        <v>0.95229523000000005</v>
+        <v>0.78917891799999995</v>
       </c>
       <c r="H4" s="2">
-        <v>3.0045575000000001E-2</v>
+        <v>0.17845148199999999</v>
       </c>
       <c r="I4" s="2">
-        <v>9.2824107000000003E-2</v>
+        <v>9.8090301000000005E-2</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K4" s="2">
-        <v>0.32918704300000001</v>
+        <v>0.55535583300000002</v>
       </c>
       <c r="L4" s="2">
-        <v>0.11259501600000001</v>
+        <v>0.15190658000000001</v>
       </c>
       <c r="M4" s="2">
-        <v>0.57033420099999999</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>0.50805836599999998</v>
+        <v>0.71784324499999996</v>
       </c>
       <c r="O4" s="2">
-        <v>0.77854723599999998</v>
+        <v>6.8513888999999994E-2</v>
       </c>
       <c r="P4" s="2">
-        <v>0.80851168699999998</v>
+        <v>0.50262433399999995</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -4747,49 +4747,49 @@
         <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2">
-        <v>0.84905660400000005</v>
+        <v>0.67295597500000004</v>
       </c>
       <c r="E5" s="2">
-        <v>0.50714285699999995</v>
+        <v>0.13571428599999999</v>
       </c>
       <c r="F5" s="2">
-        <v>0.194320357</v>
+        <v>0.17645181900000001</v>
       </c>
       <c r="G5" s="2">
-        <v>0.96659666</v>
+        <v>0.39343934400000002</v>
       </c>
       <c r="H5" s="2">
-        <v>7.7511843999999996E-2</v>
+        <v>0.18398489900000001</v>
       </c>
       <c r="I5" s="2">
-        <v>0.196932525</v>
+        <v>9.1832645000000004E-2</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="2">
-        <v>0.33745886000000003</v>
+        <v>0.82139638199999998</v>
       </c>
       <c r="L5" s="2">
-        <v>7.8070387000000005E-2</v>
+        <v>6.2002199000000001E-2</v>
       </c>
       <c r="M5" s="2">
-        <v>0.48764195799999999</v>
+        <v>0.44052065699999998</v>
       </c>
       <c r="N5" s="2">
-        <v>0.90241119599999997</v>
+        <v>0.77337964000000003</v>
       </c>
       <c r="O5" s="2">
-        <v>0.53012108400000002</v>
+        <v>0.485148142</v>
       </c>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>0.40795188100000002</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -4803,49 +4803,49 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2">
-        <v>0.67295597500000004</v>
+        <v>0.88679245299999998</v>
       </c>
       <c r="E6" s="2">
-        <v>0.59285714300000003</v>
+        <v>0.3</v>
       </c>
       <c r="F6" s="2">
-        <v>1.5954052E-2</v>
+        <v>6.3709848999999999E-2</v>
       </c>
       <c r="G6" s="2">
-        <v>0.41484148399999998</v>
+        <v>0.13821382099999999</v>
       </c>
       <c r="H6" s="2">
-        <v>0.42652304099999999</v>
+        <v>0.44640527699999999</v>
       </c>
       <c r="I6" s="2">
-        <v>0.92272049599999995</v>
+        <v>0.87965608699999998</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="2">
-        <v>0.401256218</v>
+        <v>0.35071385300000002</v>
       </c>
       <c r="L6" s="2">
-        <v>0.27005283099999999</v>
+        <v>0.28528967399999999</v>
       </c>
       <c r="M6" s="2">
-        <v>0.45252966500000003</v>
+        <v>0.39543953700000001</v>
       </c>
       <c r="N6" s="2">
-        <v>3.8906761999999998E-2</v>
+        <v>0.92930501200000004</v>
       </c>
       <c r="O6" s="2">
-        <v>0.464785956</v>
+        <v>0.561255485</v>
       </c>
       <c r="P6" s="2">
-        <v>0.28169297199999999</v>
+        <v>0.44906817700000001</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -4859,49 +4859,49 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="D7" s="2">
-        <v>0.58490565999999999</v>
+        <v>0.71698113200000002</v>
       </c>
       <c r="E7" s="2">
-        <v>0.86428571399999998</v>
+        <v>0.62857142899999996</v>
       </c>
       <c r="F7" s="2">
-        <v>0.37002765399999998</v>
+        <v>0.69336311399999995</v>
       </c>
       <c r="G7" s="2">
-        <v>0.65766576700000001</v>
+        <v>0.87208720900000003</v>
       </c>
       <c r="H7" s="2">
-        <v>0.453898107</v>
+        <v>0.33550995700000003</v>
       </c>
       <c r="I7" s="2">
-        <v>0.64613318399999997</v>
+        <v>0.63325053600000003</v>
       </c>
       <c r="J7" s="2">
-        <v>0.16666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2">
-        <v>0.204130951</v>
+        <v>0.21098535900000001</v>
       </c>
       <c r="L7" s="2">
-        <v>0.318105429</v>
+        <v>0.22895045</v>
       </c>
       <c r="M7" s="2">
-        <v>0.89785952899999999</v>
+        <v>0.62835392499999998</v>
       </c>
       <c r="N7" s="2">
-        <v>0.50225705200000004</v>
+        <v>0.61310284400000004</v>
       </c>
       <c r="O7" s="2">
-        <v>0.53658487300000002</v>
+        <v>4.4648634E-2</v>
       </c>
       <c r="P7" s="2">
-        <v>0</v>
+        <v>0.21149828200000001</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -4971,49 +4971,49 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="D9" s="2">
-        <v>0.56603773599999996</v>
+        <v>0.76729559700000005</v>
       </c>
       <c r="E9" s="2">
-        <v>0.514285714</v>
+        <v>0.61428571399999998</v>
       </c>
       <c r="F9" s="2">
-        <v>0.47415443499999999</v>
+        <v>0.26632631400000001</v>
       </c>
       <c r="G9" s="2">
-        <v>0.92449244900000005</v>
+        <v>0.33993399299999999</v>
       </c>
       <c r="H9" s="2">
-        <v>0.23632636000000001</v>
+        <v>0.20473272100000001</v>
       </c>
       <c r="I9" s="2">
-        <v>0.52037455799999999</v>
+        <v>0.61361786699999998</v>
       </c>
       <c r="J9" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="2">
-        <v>0.304510155</v>
+        <v>0.89546137000000003</v>
       </c>
       <c r="L9" s="2">
-        <v>0.106558085</v>
+        <v>1.3027375000000001E-2</v>
       </c>
       <c r="M9" s="2">
-        <v>0.45292009100000002</v>
+        <v>0.78359906000000001</v>
       </c>
       <c r="N9" s="2">
-        <v>0.75699143800000002</v>
+        <v>0.97589071900000002</v>
       </c>
       <c r="O9" s="2">
-        <v>0.70577476900000002</v>
+        <v>0.92274844099999997</v>
       </c>
       <c r="P9" s="2">
-        <v>0.78043004299999996</v>
+        <v>0.41731044099999998</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -5027,49 +5027,49 @@
         <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2">
-        <v>0.71069182399999997</v>
+        <v>0.93710691800000001</v>
       </c>
       <c r="E10" s="2">
-        <v>0.36428571399999998</v>
+        <v>0.52142857099999995</v>
       </c>
       <c r="F10" s="2">
-        <v>0.36832588799999999</v>
+        <v>7.2856839000000007E-2</v>
       </c>
       <c r="G10" s="2">
-        <v>0.31673167299999999</v>
+        <v>7.4707470999999998E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.18603947200000001</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0.34127542300000002</v>
+        <v>6.2041530999999997E-2</v>
       </c>
       <c r="J10" s="2">
-        <v>0.33333333300000001</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2">
-        <v>0.46809305800000001</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2">
-        <v>5.5607701000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>0.78997805200000004</v>
+        <v>0.77758418600000001</v>
       </c>
       <c r="N10" s="2">
-        <v>0.906299933</v>
+        <v>0.97796258599999997</v>
       </c>
       <c r="O10" s="2">
-        <v>1</v>
+        <v>0.99829236799999999</v>
       </c>
       <c r="P10" s="2">
-        <v>0.45592408000000001</v>
+        <v>0.54080612500000003</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -5083,49 +5083,49 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2">
-        <v>0.421383648</v>
+        <v>0.93710691800000001</v>
       </c>
       <c r="E11" s="2">
-        <v>0.43571428600000001</v>
+        <v>0.31428571399999999</v>
       </c>
       <c r="F11" s="2">
-        <v>0.432142097</v>
+        <v>0.17592001700000001</v>
       </c>
       <c r="G11" s="2">
-        <v>0.54105410499999995</v>
+        <v>0.17381738199999999</v>
       </c>
       <c r="H11" s="2">
-        <v>0.34989293199999999</v>
+        <v>0.31666840499999999</v>
       </c>
       <c r="I11" s="2">
-        <v>0.49046524600000002</v>
+        <v>0.35383240700000002</v>
       </c>
       <c r="J11" s="2">
-        <v>0.16666666699999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K11" s="2">
-        <v>0.25221986499999999</v>
+        <v>0.77403714800000001</v>
       </c>
       <c r="L11" s="2">
-        <v>0.12821922499999999</v>
+        <v>0.115708833</v>
       </c>
       <c r="M11" s="2">
-        <v>1</v>
+        <v>0.60377196099999997</v>
       </c>
       <c r="N11" s="2">
-        <v>0.44259828600000001</v>
+        <v>0.74903278500000003</v>
       </c>
       <c r="O11" s="2">
-        <v>0.27935531200000002</v>
+        <v>0.95889473999999997</v>
       </c>
       <c r="P11" s="2">
-        <v>0.11926938500000001</v>
+        <v>0.47668356299999998</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -5139,49 +5139,49 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2">
-        <v>0.86792452799999997</v>
+        <v>0.71069182399999997</v>
       </c>
       <c r="E12" s="2">
-        <v>0.47857142899999999</v>
+        <v>0.36428571399999998</v>
       </c>
       <c r="F12" s="2">
-        <v>0.65241437999999996</v>
+        <v>0.36832588799999999</v>
       </c>
       <c r="G12" s="2">
-        <v>0.98189819</v>
+        <v>0.31673167299999999</v>
       </c>
       <c r="H12" s="2">
-        <v>0.117479163</v>
+        <v>0.18603947200000001</v>
       </c>
       <c r="I12" s="2">
-        <v>0.24837313</v>
+        <v>0.34127542300000002</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K12" s="2">
-        <v>0.27112415099999998</v>
+        <v>0.46809305800000001</v>
       </c>
       <c r="L12" s="2">
-        <v>0.104232407</v>
+        <v>5.5607701000000002E-2</v>
       </c>
       <c r="M12" s="2">
-        <v>0.52805239500000001</v>
+        <v>0.78997805200000004</v>
       </c>
       <c r="N12" s="2">
-        <v>0.71972293200000004</v>
+        <v>0.906299933</v>
       </c>
       <c r="O12" s="2">
-        <v>0.63764200500000001</v>
+        <v>1</v>
       </c>
       <c r="P12" s="2">
-        <v>0.74866072900000002</v>
+        <v>0.45592408000000001</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -5195,49 +5195,49 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2">
-        <v>0.66666666699999999</v>
+        <v>0.74213836499999997</v>
       </c>
       <c r="E13" s="2">
-        <v>0.69285714300000001</v>
+        <v>0.61428571399999998</v>
       </c>
       <c r="F13" s="2">
-        <v>0.113167411</v>
+        <v>0.23697085700000001</v>
       </c>
       <c r="G13" s="2">
-        <v>0.90999099900000002</v>
+        <v>0.50385038500000001</v>
       </c>
       <c r="H13" s="2">
-        <v>0.33086383000000003</v>
+        <v>0.459307097</v>
       </c>
       <c r="I13" s="2">
-        <v>0.76193436800000003</v>
+        <v>0.66037053099999998</v>
       </c>
       <c r="J13" s="2">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K13" s="2">
-        <v>0.302855029</v>
+        <v>0.336819437</v>
       </c>
       <c r="L13" s="2">
-        <v>0.22286882299999999</v>
+        <v>0.28363294500000003</v>
       </c>
       <c r="M13" s="2">
-        <v>0.52045348000000002</v>
+        <v>0.76582151300000001</v>
       </c>
       <c r="N13" s="2">
-        <v>0.19729364999999999</v>
+        <v>0.64434333600000004</v>
       </c>
       <c r="O13" s="2">
-        <v>0.57005088400000004</v>
+        <v>0.74571350999999997</v>
       </c>
       <c r="P13" s="2">
-        <v>0.55794312499999998</v>
+        <v>2.5430277000000001E-2</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -5251,49 +5251,49 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="D14" s="2">
-        <v>0.106918239</v>
+        <v>0.62893081799999995</v>
       </c>
       <c r="E14" s="2">
-        <v>0.75714285699999995</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="2">
-        <v>0.96777281400000004</v>
+        <v>0.24686237</v>
       </c>
       <c r="G14" s="2">
-        <v>0.99959995999999995</v>
+        <v>0.70307030699999995</v>
       </c>
       <c r="H14" s="2">
-        <v>0.23070697000000001</v>
+        <v>0.55808644399999996</v>
       </c>
       <c r="I14" s="2">
-        <v>0.51241333700000002</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2">
         <v>0</v>
       </c>
       <c r="K14" s="2">
-        <v>4.0751442999999998E-2</v>
+        <v>0.292028063</v>
       </c>
       <c r="L14" s="2">
-        <v>0.29681377599999997</v>
+        <v>0.18962547799999999</v>
       </c>
       <c r="M14" s="2">
-        <v>0.52896455399999998</v>
+        <v>0.705715596</v>
       </c>
       <c r="N14" s="2">
-        <v>0.34160277</v>
+        <v>0.70047848800000001</v>
       </c>
       <c r="O14" s="2">
-        <v>0.27884996899999998</v>
+        <v>0.49197468900000002</v>
       </c>
       <c r="P14" s="2">
-        <v>5.9376028999999997E-2</v>
+        <v>0.103590684</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -5307,49 +5307,49 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2">
-        <v>0.94339622599999995</v>
+        <v>0.58490565999999999</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2</v>
+        <v>0.86428571399999998</v>
       </c>
       <c r="F15" s="2">
-        <v>0.31652839799999999</v>
+        <v>0.37002765399999998</v>
       </c>
       <c r="G15" s="2">
-        <v>0.78917891799999995</v>
+        <v>0.65766576700000001</v>
       </c>
       <c r="H15" s="2">
-        <v>0.17845148199999999</v>
+        <v>0.453898107</v>
       </c>
       <c r="I15" s="2">
-        <v>9.8090301000000005E-2</v>
+        <v>0.64613318399999997</v>
       </c>
       <c r="J15" s="2">
         <v>0.16666666699999999</v>
       </c>
       <c r="K15" s="2">
-        <v>0.55535583300000002</v>
+        <v>0.204130951</v>
       </c>
       <c r="L15" s="2">
-        <v>0.15190658000000001</v>
+        <v>0.318105429</v>
       </c>
       <c r="M15" s="2">
-        <v>0</v>
+        <v>0.89785952899999999</v>
       </c>
       <c r="N15" s="2">
-        <v>0.71784324499999996</v>
+        <v>0.50225705200000004</v>
       </c>
       <c r="O15" s="2">
-        <v>6.8513888999999994E-2</v>
+        <v>0.53658487300000002</v>
       </c>
       <c r="P15" s="2">
-        <v>0.50262433399999995</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -5363,49 +5363,49 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2">
-        <v>0.364779874</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>0.928571429</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F16" s="2">
-        <v>0.209636248</v>
+        <v>7.9663900999999995E-2</v>
       </c>
       <c r="G16" s="2">
-        <v>0.98779877999999999</v>
+        <v>1.4801480000000001E-2</v>
       </c>
       <c r="H16" s="2">
-        <v>0.68614056599999995</v>
+        <v>0.59174899999999997</v>
       </c>
       <c r="I16" s="2">
-        <v>0.33756884399999998</v>
+        <v>0.47860433899999999</v>
       </c>
       <c r="J16" s="2">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K16" s="2">
-        <v>9.4689231999999998E-2</v>
+        <v>0.43742491900000002</v>
       </c>
       <c r="L16" s="2">
-        <v>0.25616878399999998</v>
+        <v>9.8116513000000002E-2</v>
       </c>
       <c r="M16" s="2">
-        <v>0.48154087299999998</v>
+        <v>0.65263081700000003</v>
       </c>
       <c r="N16" s="2">
-        <v>0.41338075200000002</v>
+        <v>0.72849704800000004</v>
       </c>
       <c r="O16" s="2">
-        <v>0.53817268100000004</v>
+        <v>0.63622342099999996</v>
       </c>
       <c r="P16" s="2">
-        <v>6.5072617999999999E-2</v>
+        <v>0.13152203900000001</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -5419,49 +5419,49 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2">
-        <v>0.54088050300000001</v>
+        <v>0.62893081799999995</v>
       </c>
       <c r="E17" s="2">
-        <v>0.74285714300000005</v>
+        <v>0.735714286</v>
       </c>
       <c r="F17" s="2">
-        <v>0.41863433300000003</v>
+        <v>0.68836417800000005</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>0.76757675800000003</v>
       </c>
       <c r="H17" s="2">
-        <v>9.8367679E-2</v>
+        <v>0.379062169</v>
       </c>
       <c r="I17" s="2">
-        <v>0.86225275000000001</v>
+        <v>0.12726075000000001</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
       </c>
       <c r="K17" s="2">
-        <v>0.30548390800000003</v>
+        <v>0.20493054699999999</v>
       </c>
       <c r="L17" s="2">
-        <v>0.17419346199999999</v>
+        <v>0.29458642899999998</v>
       </c>
       <c r="M17" s="2">
-        <v>0.42225821200000002</v>
+        <v>0.854762299</v>
       </c>
       <c r="N17" s="2">
-        <v>0.73988199099999996</v>
+        <v>0.47480983100000002</v>
       </c>
       <c r="O17" s="2">
-        <v>0.56049442500000002</v>
+        <v>0.29526159800000001</v>
       </c>
       <c r="P17" s="2">
-        <v>0.72621669600000005</v>
+        <v>5.5999519999999997E-2</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -5475,49 +5475,49 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2">
-        <v>0.51572326999999996</v>
+        <v>0.80503144699999996</v>
       </c>
       <c r="E18" s="2">
-        <v>0.59285714300000003</v>
+        <v>0.85</v>
       </c>
       <c r="F18" s="2">
-        <v>0.59636247600000003</v>
+        <v>0.31908104700000001</v>
       </c>
       <c r="G18" s="2">
-        <v>0.98899890000000001</v>
+        <v>0.55675567599999998</v>
       </c>
       <c r="H18" s="2">
-        <v>0.183564428</v>
+        <v>0.45028653899999999</v>
       </c>
       <c r="I18" s="2">
-        <v>0.98518585199999997</v>
+        <v>0.55215021099999995</v>
       </c>
       <c r="J18" s="2">
-        <v>0</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K18" s="2">
-        <v>0.176834082</v>
+        <v>0.29110007399999999</v>
       </c>
       <c r="L18" s="2">
-        <v>0.274197633</v>
+        <v>9.5050371999999994E-2</v>
       </c>
       <c r="M18" s="2">
-        <v>0.45004276599999998</v>
+        <v>0.71449521500000002</v>
       </c>
       <c r="N18" s="2">
-        <v>0.64907111200000001</v>
+        <v>0.64627516500000004</v>
       </c>
       <c r="O18" s="2">
-        <v>0.60666912399999995</v>
+        <v>0.48545434900000001</v>
       </c>
       <c r="P18" s="2">
-        <v>0.73151146700000003</v>
+        <v>3.1770394E-2</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -5531,49 +5531,49 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>0.49685534599999998</v>
       </c>
       <c r="E19" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.985714286</v>
       </c>
       <c r="F19" s="2">
-        <v>7.9663900999999995E-2</v>
+        <v>0.63582216499999999</v>
       </c>
       <c r="G19" s="2">
-        <v>1.4801480000000001E-2</v>
+        <v>0.51915191500000002</v>
       </c>
       <c r="H19" s="2">
-        <v>0.59174899999999997</v>
+        <v>0.28133235000000001</v>
       </c>
       <c r="I19" s="2">
-        <v>0.47860433899999999</v>
+        <v>0.101473614</v>
       </c>
       <c r="J19" s="2">
-        <v>0.33333333300000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2">
-        <v>0.43742491900000002</v>
+        <v>0.15519667700000001</v>
       </c>
       <c r="L19" s="2">
-        <v>9.8116513000000002E-2</v>
+        <v>0.29483076600000002</v>
       </c>
       <c r="M19" s="2">
-        <v>0.65263081700000003</v>
+        <v>0.58237165999999996</v>
       </c>
       <c r="N19" s="2">
-        <v>0.72849704800000004</v>
+        <v>1.207182E-3</v>
       </c>
       <c r="O19" s="2">
-        <v>0.63622342099999996</v>
+        <v>0.63631287400000003</v>
       </c>
       <c r="P19" s="2">
-        <v>0.13152203900000001</v>
+        <v>0.17800613900000001</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -5587,49 +5587,49 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D20" s="2">
-        <v>0.96855345900000001</v>
+        <v>0.22641509400000001</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2">
-        <v>0.31078493899999998</v>
+        <v>0.88789619200000003</v>
       </c>
       <c r="G20" s="2">
-        <v>0.62266226599999996</v>
+        <v>0.99439944000000002</v>
       </c>
       <c r="H20" s="2">
-        <v>9.5431956999999998E-2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>0.51024906000000003</v>
       </c>
       <c r="J20" s="2">
-        <v>0.33333333300000001</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K20" s="2">
-        <v>0.531891687</v>
+        <v>9.7197345000000004E-2</v>
       </c>
       <c r="L20" s="2">
-        <v>0.144734372</v>
+        <v>0.32635778799999998</v>
       </c>
       <c r="M20" s="2">
-        <v>0.20195196300000001</v>
+        <v>0.60439305799999998</v>
       </c>
       <c r="N20" s="2">
-        <v>0.79734716800000005</v>
+        <v>0.175036893</v>
       </c>
       <c r="O20" s="2">
-        <v>0.192511933</v>
+        <v>0.62954073300000002</v>
       </c>
       <c r="P20" s="2">
-        <v>0.491921049</v>
+        <v>0.17823530900000001</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -5643,49 +5643,49 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2">
-        <v>0.53459119499999996</v>
+        <v>0.364779874</v>
       </c>
       <c r="E21" s="2">
-        <v>0.735714286</v>
+        <v>0.928571429</v>
       </c>
       <c r="F21" s="2">
-        <v>0.223463093</v>
+        <v>0.209636248</v>
       </c>
       <c r="G21" s="2">
-        <v>0.34723472300000002</v>
+        <v>0.98779877999999999</v>
       </c>
       <c r="H21" s="2">
-        <v>0.26406674000000002</v>
+        <v>0.68614056599999995</v>
       </c>
       <c r="I21" s="2">
-        <v>0.65472615999999995</v>
+        <v>0.33756884399999998</v>
       </c>
       <c r="J21" s="2">
-        <v>0.16666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2">
-        <v>0.24477179700000001</v>
+        <v>9.4689231999999998E-2</v>
       </c>
       <c r="L21" s="2">
-        <v>0.211300026</v>
+        <v>0.25616878399999998</v>
       </c>
       <c r="M21" s="2">
-        <v>0.92761738800000004</v>
+        <v>0.48154087299999998</v>
       </c>
       <c r="N21" s="2">
-        <v>0.275613102</v>
+        <v>0.41338075200000002</v>
       </c>
       <c r="O21" s="2">
-        <v>0.11924188500000001</v>
+        <v>0.53817268100000004</v>
       </c>
       <c r="P21" s="2">
-        <v>6.1743984000000002E-2</v>
+        <v>6.5072617999999999E-2</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -5699,49 +5699,49 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2">
-        <v>0.88679245299999998</v>
+        <v>0.56603773599999996</v>
       </c>
       <c r="E22" s="2">
-        <v>0.3</v>
+        <v>0.92142857099999997</v>
       </c>
       <c r="F22" s="2">
-        <v>6.3709848999999999E-2</v>
+        <v>0.24058710899999999</v>
       </c>
       <c r="G22" s="2">
-        <v>0.13821382099999999</v>
+        <v>0.97309730999999999</v>
       </c>
       <c r="H22" s="2">
-        <v>0.44640527699999999</v>
+        <v>0.37373198000000002</v>
       </c>
       <c r="I22" s="2">
-        <v>0.87965608699999998</v>
+        <v>0.32177672699999998</v>
       </c>
       <c r="J22" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2">
-        <v>0.35071385300000002</v>
+        <v>0.11069514</v>
       </c>
       <c r="L22" s="2">
-        <v>0.28528967399999999</v>
+        <v>0.23588725899999999</v>
       </c>
       <c r="M22" s="2">
-        <v>0.39543953700000001</v>
+        <v>0.62113350599999995</v>
       </c>
       <c r="N22" s="2">
-        <v>0.92930501200000004</v>
+        <v>0.31941010600000003</v>
       </c>
       <c r="O22" s="2">
-        <v>0.561255485</v>
+        <v>0.59603989800000001</v>
       </c>
       <c r="P22" s="2">
-        <v>0.44906817700000001</v>
+        <v>3.9746256000000001E-2</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -5755,49 +5755,49 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2">
-        <v>0.62893081799999995</v>
+        <v>0.106918239</v>
       </c>
       <c r="E23" s="2">
-        <v>0.735714286</v>
+        <v>0.75714285699999995</v>
       </c>
       <c r="F23" s="2">
-        <v>0.68836417800000005</v>
+        <v>0.96777281400000004</v>
       </c>
       <c r="G23" s="2">
-        <v>0.76757675800000003</v>
+        <v>0.99959995999999995</v>
       </c>
       <c r="H23" s="2">
-        <v>0.379062169</v>
+        <v>0.23070697000000001</v>
       </c>
       <c r="I23" s="2">
-        <v>0.12726075000000001</v>
+        <v>0.51241333700000002</v>
       </c>
       <c r="J23" s="2">
         <v>0</v>
       </c>
       <c r="K23" s="2">
-        <v>0.20493054699999999</v>
+        <v>4.0751442999999998E-2</v>
       </c>
       <c r="L23" s="2">
-        <v>0.29458642899999998</v>
+        <v>0.29681377599999997</v>
       </c>
       <c r="M23" s="2">
-        <v>0.854762299</v>
+        <v>0.52896455399999998</v>
       </c>
       <c r="N23" s="2">
-        <v>0.47480983100000002</v>
+        <v>0.34160277</v>
       </c>
       <c r="O23" s="2">
-        <v>0.29526159800000001</v>
+        <v>0.27884996899999998</v>
       </c>
       <c r="P23" s="2">
-        <v>5.5999519999999997E-2</v>
+        <v>5.9376028999999997E-2</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -5811,49 +5811,49 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D24" s="2">
-        <v>0.80503144699999996</v>
+        <v>0.70440251600000003</v>
       </c>
       <c r="E24" s="2">
-        <v>0.85</v>
+        <v>0.38571428600000002</v>
       </c>
       <c r="F24" s="2">
-        <v>0.31908104700000001</v>
+        <v>0.100191449</v>
       </c>
       <c r="G24" s="2">
-        <v>0.55675567599999998</v>
+        <v>8.7008700999999994E-2</v>
       </c>
       <c r="H24" s="2">
-        <v>0.45028653899999999</v>
+        <v>0.180815806</v>
       </c>
       <c r="I24" s="2">
-        <v>0.55215021099999995</v>
+        <v>0.23013325900000001</v>
       </c>
       <c r="J24" s="2">
-        <v>0.16666666699999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K24" s="2">
-        <v>0.29110007399999999</v>
+        <v>0.977321467</v>
       </c>
       <c r="L24" s="2">
-        <v>9.5050371999999994E-2</v>
+        <v>9.7733617999999994E-2</v>
       </c>
       <c r="M24" s="2">
-        <v>0.71449521500000002</v>
+        <v>0.57609191199999998</v>
       </c>
       <c r="N24" s="2">
-        <v>0.64627516500000004</v>
+        <v>0.51609956999999995</v>
       </c>
       <c r="O24" s="2">
-        <v>0.48545434900000001</v>
+        <v>0.57591988900000002</v>
       </c>
       <c r="P24" s="2">
-        <v>3.1770394E-2</v>
+        <v>0.45368767300000001</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
@@ -5867,49 +5867,49 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="D25" s="2">
-        <v>0.93710691800000001</v>
+        <v>0.80503144699999996</v>
       </c>
       <c r="E25" s="2">
-        <v>0.52142857099999995</v>
+        <v>0.34285714299999998</v>
       </c>
       <c r="F25" s="2">
-        <v>7.2856839000000007E-2</v>
+        <v>7.4984045999999999E-2</v>
       </c>
       <c r="G25" s="2">
-        <v>7.4707470999999998E-2</v>
+        <v>0.24532453200000001</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>0.23845611899999999</v>
       </c>
       <c r="I25" s="2">
-        <v>6.2041530999999997E-2</v>
+        <v>0.20531851000000001</v>
       </c>
       <c r="J25" s="2">
-        <v>1</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
+        <v>0.802331923</v>
       </c>
       <c r="L25" s="2">
-        <v>0</v>
+        <v>9.4862648999999993E-2</v>
       </c>
       <c r="M25" s="2">
-        <v>0.77758418600000001</v>
+        <v>0.465835628</v>
       </c>
       <c r="N25" s="2">
-        <v>0.97796258599999997</v>
+        <v>0.33325132099999999</v>
       </c>
       <c r="O25" s="2">
-        <v>0.99829236799999999</v>
+        <v>0.198697084</v>
       </c>
       <c r="P25" s="2">
-        <v>0.54080612500000003</v>
+        <v>0.13909770499999999</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -5923,49 +5923,49 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D26" s="2">
-        <v>0.93710691800000001</v>
+        <v>0.59748427699999995</v>
       </c>
       <c r="E26" s="2">
-        <v>0.31428571399999999</v>
+        <v>0.27857142899999998</v>
       </c>
       <c r="F26" s="2">
-        <v>0.17592001700000001</v>
+        <v>1.9357583000000001E-2</v>
       </c>
       <c r="G26" s="2">
-        <v>0.17381738199999999</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>0.31666840499999999</v>
+        <v>0.42644246600000002</v>
       </c>
       <c r="I26" s="2">
-        <v>0.35383240700000002</v>
+        <v>0.27924324099999998</v>
       </c>
       <c r="J26" s="2">
-        <v>0.66666666699999999</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K26" s="2">
-        <v>0.77403714800000001</v>
+        <v>0.85792992300000004</v>
       </c>
       <c r="L26" s="2">
-        <v>0.115708833</v>
+        <v>4.957226E-2</v>
       </c>
       <c r="M26" s="2">
-        <v>0.60377196099999997</v>
+        <v>0.81324384800000005</v>
       </c>
       <c r="N26" s="2">
-        <v>0.74903278500000003</v>
+        <v>0.66339290500000003</v>
       </c>
       <c r="O26" s="2">
-        <v>0.95889473999999997</v>
+        <v>0.36603221600000002</v>
       </c>
       <c r="P26" s="2">
-        <v>0.47668356299999998</v>
+        <v>0.35513536200000001</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
@@ -5979,49 +5979,49 @@
         <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2">
-        <v>0.74213836499999997</v>
+        <v>0.75471698099999995</v>
       </c>
       <c r="E27" s="2">
         <v>0.61428571399999998</v>
       </c>
       <c r="F27" s="2">
-        <v>0.23697085700000001</v>
+        <v>0.30344607499999998</v>
       </c>
       <c r="G27" s="2">
-        <v>0.50385038500000001</v>
+        <v>0.88368836900000003</v>
       </c>
       <c r="H27" s="2">
-        <v>0.459307097</v>
+        <v>0.132620195</v>
       </c>
       <c r="I27" s="2">
-        <v>0.66037053099999998</v>
+        <v>0.39791784499999999</v>
       </c>
       <c r="J27" s="2">
-        <v>0.33333333300000001</v>
+        <v>0</v>
       </c>
       <c r="K27" s="2">
-        <v>0.336819437</v>
+        <v>0.25299276500000001</v>
       </c>
       <c r="L27" s="2">
-        <v>0.28363294500000003</v>
+        <v>0.17769315299999999</v>
       </c>
       <c r="M27" s="2">
-        <v>0.76582151300000001</v>
+        <v>0.50065998099999998</v>
       </c>
       <c r="N27" s="2">
-        <v>0.64434333600000004</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2">
-        <v>0.74571350999999997</v>
+        <v>0.65095266399999996</v>
       </c>
       <c r="P27" s="2">
-        <v>2.5430277000000001E-2</v>
+        <v>0.19335734500000001</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
@@ -6035,49 +6035,49 @@
         <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D28" s="2">
-        <v>0.69182389899999996</v>
+        <v>0.371069182</v>
       </c>
       <c r="E28" s="2">
-        <v>0.39285714300000002</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="F28" s="2">
-        <v>0.45341416699999998</v>
+        <v>0.38672622800000001</v>
       </c>
       <c r="G28" s="2">
-        <v>0.93179317900000003</v>
+        <v>0.97609760999999995</v>
       </c>
       <c r="H28" s="2">
-        <v>0.21596468199999999</v>
+        <v>0.14198671600000001</v>
       </c>
       <c r="I28" s="2">
-        <v>0.61653771800000001</v>
+        <v>0.34739539200000003</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
       </c>
       <c r="K28" s="2">
-        <v>0.39129240900000001</v>
+        <v>0.17040426</v>
       </c>
       <c r="L28" s="2">
-        <v>8.7891574E-2</v>
+        <v>0.25675281100000003</v>
       </c>
       <c r="M28" s="2">
-        <v>0.40564392900000001</v>
+        <v>0.53521248499999996</v>
       </c>
       <c r="N28" s="2">
-        <v>0.87772592599999999</v>
+        <v>0.116742658</v>
       </c>
       <c r="O28" s="2">
-        <v>0.65187830300000005</v>
+        <v>0.62536076500000004</v>
       </c>
       <c r="P28" s="2">
-        <v>0.88580566699999996</v>
+        <v>0.34743216700000001</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
@@ -6091,49 +6091,49 @@
         <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D29" s="2">
-        <v>0.30188679200000001</v>
+        <v>0.67295597500000004</v>
       </c>
       <c r="E29" s="2">
-        <v>0.492857143</v>
+        <v>0.59285714300000003</v>
       </c>
       <c r="F29" s="2">
-        <v>0.95288236500000001</v>
+        <v>1.5954052E-2</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>0.41484148399999998</v>
       </c>
       <c r="H29" s="2">
-        <v>0.35188138699999999</v>
+        <v>0.42652304099999999</v>
       </c>
       <c r="I29" s="2">
-        <v>0.61653771800000001</v>
+        <v>0.92272049599999995</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
       </c>
       <c r="K29" s="2">
-        <v>0.12986002599999999</v>
+        <v>0.401256218</v>
       </c>
       <c r="L29" s="2">
-        <v>0.60092788799999997</v>
+        <v>0.27005283099999999</v>
       </c>
       <c r="M29" s="2">
-        <v>5.1697329E-2</v>
+        <v>0.45252966500000003</v>
       </c>
       <c r="N29" s="2">
-        <v>0.67434201100000002</v>
+        <v>3.8906761999999998E-2</v>
       </c>
       <c r="O29" s="2">
-        <v>0</v>
+        <v>0.464785956</v>
       </c>
       <c r="P29" s="2">
-        <v>0.49508760099999999</v>
+        <v>0.28169297199999999</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -6147,49 +6147,49 @@
         <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D30" s="2">
-        <v>0.56603773599999996</v>
+        <v>0.69182389899999996</v>
       </c>
       <c r="E30" s="2">
-        <v>0.92142857099999997</v>
+        <v>0.62857142899999996</v>
       </c>
       <c r="F30" s="2">
-        <v>0.24058710899999999</v>
+        <v>2.0952989000000002E-2</v>
       </c>
       <c r="G30" s="2">
-        <v>0.97309730999999999</v>
+        <v>0.82918291799999999</v>
       </c>
       <c r="H30" s="2">
-        <v>0.37373198000000002</v>
+        <v>0.304217609</v>
       </c>
       <c r="I30" s="2">
-        <v>0.32177672699999998</v>
+        <v>0.20844248700000001</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>0.11069514</v>
+        <v>0.29364632400000001</v>
       </c>
       <c r="L30" s="2">
-        <v>0.23588725899999999</v>
+        <v>0.20058939000000001</v>
       </c>
       <c r="M30" s="2">
-        <v>0.62113350599999995</v>
+        <v>0.45401219799999998</v>
       </c>
       <c r="N30" s="2">
-        <v>0.31941010600000003</v>
+        <v>0.40062268699999998</v>
       </c>
       <c r="O30" s="2">
-        <v>0.59603989800000001</v>
+        <v>0.67107552100000001</v>
       </c>
       <c r="P30" s="2">
-        <v>3.9746256000000001E-2</v>
+        <v>0.57342699699999999</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -6203,49 +6203,49 @@
         <v>16</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
-        <v>0</v>
+        <v>0.66037735799999997</v>
       </c>
       <c r="E31" s="2">
-        <v>0.65714285699999997</v>
+        <v>0.61428571399999998</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>0.14592639900000001</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>0.58025802599999998</v>
       </c>
       <c r="H31" s="2">
-        <v>0.242252783</v>
+        <v>0.516404643</v>
       </c>
       <c r="I31" s="2">
-        <v>0.29161058299999998</v>
+        <v>0.34610756100000001</v>
       </c>
       <c r="J31" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K31" s="2">
-        <v>0</v>
+        <v>0.562139053</v>
       </c>
       <c r="L31" s="2">
-        <v>1</v>
+        <v>8.8109093999999999E-2</v>
       </c>
       <c r="M31" s="2">
-        <v>0.62093195999999995</v>
+        <v>0.59576597600000003</v>
       </c>
       <c r="N31" s="2">
-        <v>0.31168562599999999</v>
+        <v>0.28821811400000003</v>
       </c>
       <c r="O31" s="2">
-        <v>0.213706174</v>
+        <v>0.26039265900000003</v>
       </c>
       <c r="P31" s="2">
-        <v>0.113557749</v>
+        <v>0.312149079</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
@@ -6259,49 +6259,49 @@
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2">
-        <v>0.49685534599999998</v>
+        <v>0.53459119499999996</v>
       </c>
       <c r="E32" s="2">
-        <v>0.75</v>
+        <v>0.735714286</v>
       </c>
       <c r="F32" s="2">
-        <v>0.58168474800000003</v>
+        <v>0.223463093</v>
       </c>
       <c r="G32" s="2">
-        <v>0.96109610999999995</v>
+        <v>0.34723472300000002</v>
       </c>
       <c r="H32" s="2">
-        <v>0.209358249</v>
+        <v>0.26406674000000002</v>
       </c>
       <c r="I32" s="2">
-        <v>0.39034780600000002</v>
+        <v>0.65472615999999995</v>
       </c>
       <c r="J32" s="2">
-        <v>0</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K32" s="2">
-        <v>0.191460719</v>
+        <v>0.24477179700000001</v>
       </c>
       <c r="L32" s="2">
-        <v>0.30904109299999999</v>
+        <v>0.211300026</v>
       </c>
       <c r="M32" s="2">
-        <v>0.67763728899999998</v>
+        <v>0.92761738800000004</v>
       </c>
       <c r="N32" s="2">
-        <v>0.133937633</v>
+        <v>0.275613102</v>
       </c>
       <c r="O32" s="2">
-        <v>0.361793535</v>
+        <v>0.11924188500000001</v>
       </c>
       <c r="P32" s="2">
-        <v>0.23195674299999999</v>
+        <v>6.1743984000000002E-2</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
@@ -6315,49 +6315,49 @@
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2">
-        <v>0.69182389899999996</v>
+        <v>0.49685534599999998</v>
       </c>
       <c r="E33" s="2">
-        <v>0.62857142899999996</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="2">
-        <v>2.0952989000000002E-2</v>
+        <v>0.58168474800000003</v>
       </c>
       <c r="G33" s="2">
-        <v>0.82918291799999999</v>
+        <v>0.96109610999999995</v>
       </c>
       <c r="H33" s="2">
-        <v>0.304217609</v>
+        <v>0.209358249</v>
       </c>
       <c r="I33" s="2">
-        <v>0.20844248700000001</v>
+        <v>0.39034780600000002</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>0.29364632400000001</v>
+        <v>0.191460719</v>
       </c>
       <c r="L33" s="2">
-        <v>0.20058939000000001</v>
+        <v>0.30904109299999999</v>
       </c>
       <c r="M33" s="2">
-        <v>0.45401219799999998</v>
+        <v>0.67763728899999998</v>
       </c>
       <c r="N33" s="2">
-        <v>0.40062268699999998</v>
+        <v>0.133937633</v>
       </c>
       <c r="O33" s="2">
-        <v>0.67107552100000001</v>
+        <v>0.361793535</v>
       </c>
       <c r="P33" s="2">
-        <v>0.57342699699999999</v>
+        <v>0.23195674299999999</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
@@ -6427,49 +6427,49 @@
         <v>16</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2">
-        <v>0.553459119</v>
+        <v>0.421383648</v>
       </c>
       <c r="E35" s="2">
-        <v>0.821428571</v>
+        <v>0.43571428600000001</v>
       </c>
       <c r="F35" s="2">
-        <v>0.32429270399999999</v>
+        <v>0.432142097</v>
       </c>
       <c r="G35" s="2">
-        <v>0.98799879999999995</v>
+        <v>0.54105410499999995</v>
       </c>
       <c r="H35" s="2">
-        <v>0.30755589799999999</v>
+        <v>0.34989293199999999</v>
       </c>
       <c r="I35" s="2">
-        <v>0.54020447599999999</v>
+        <v>0.49046524600000002</v>
       </c>
       <c r="J35" s="2">
-        <v>0</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K35" s="2">
-        <v>0.281559581</v>
+        <v>0.25221986499999999</v>
       </c>
       <c r="L35" s="2">
-        <v>0.22729968</v>
+        <v>0.12821922499999999</v>
       </c>
       <c r="M35" s="2">
-        <v>0.46549512900000001</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2">
-        <v>0.51425926600000005</v>
+        <v>0.44259828600000001</v>
       </c>
       <c r="O35" s="2">
-        <v>0.52002510899999999</v>
+        <v>0.27935531200000002</v>
       </c>
       <c r="P35" s="2">
-        <v>0.63646293399999998</v>
+        <v>0.11926938500000001</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
@@ -6483,49 +6483,49 @@
         <v>16</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
-        <v>0.49685534599999998</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="E36" s="2">
-        <v>0.985714286</v>
+        <v>0.69285714300000001</v>
       </c>
       <c r="F36" s="2">
-        <v>0.63582216499999999</v>
+        <v>0.113167411</v>
       </c>
       <c r="G36" s="2">
-        <v>0.51915191500000002</v>
+        <v>0.90999099900000002</v>
       </c>
       <c r="H36" s="2">
-        <v>0.28133235000000001</v>
+        <v>0.33086383000000003</v>
       </c>
       <c r="I36" s="2">
-        <v>0.101473614</v>
+        <v>0.76193436800000003</v>
       </c>
       <c r="J36" s="2">
         <v>0</v>
       </c>
       <c r="K36" s="2">
-        <v>0.15519667700000001</v>
+        <v>0.302855029</v>
       </c>
       <c r="L36" s="2">
-        <v>0.29483076600000002</v>
+        <v>0.22286882299999999</v>
       </c>
       <c r="M36" s="2">
-        <v>0.58237165999999996</v>
+        <v>0.52045348000000002</v>
       </c>
       <c r="N36" s="2">
-        <v>1.207182E-3</v>
+        <v>0.19729364999999999</v>
       </c>
       <c r="O36" s="2">
-        <v>0.63631287400000003</v>
+        <v>0.57005088400000004</v>
       </c>
       <c r="P36" s="2">
-        <v>0.17800613900000001</v>
+        <v>0.55794312499999998</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
@@ -6539,49 +6539,49 @@
         <v>16</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2">
-        <v>0.22641509400000001</v>
+        <v>0.75471698099999995</v>
       </c>
       <c r="E37" s="2">
-        <v>1</v>
+        <v>0.62142857100000004</v>
       </c>
       <c r="F37" s="2">
-        <v>0.88789619200000003</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
-        <v>0.99439944000000002</v>
+        <v>0.56295629599999997</v>
       </c>
       <c r="H37" s="2">
-        <v>1</v>
+        <v>0.146887608</v>
       </c>
       <c r="I37" s="2">
-        <v>0.51024906000000003</v>
+        <v>7.6667902999999996E-2</v>
       </c>
       <c r="J37" s="2">
-        <v>0.16666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2">
-        <v>9.7197345000000004E-2</v>
+        <v>0.27595732299999998</v>
       </c>
       <c r="L37" s="2">
-        <v>0.32635778799999998</v>
+        <v>0.21956430399999999</v>
       </c>
       <c r="M37" s="2">
-        <v>0.60439305799999998</v>
+        <v>0.56511400899999997</v>
       </c>
       <c r="N37" s="2">
-        <v>0.175036893</v>
+        <v>0.27506281599999999</v>
       </c>
       <c r="O37" s="2">
-        <v>0.62954073300000002</v>
+        <v>0.68108515999999997</v>
       </c>
       <c r="P37" s="2">
-        <v>0.17823530900000001</v>
+        <v>0.65638742400000005</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
@@ -6595,49 +6595,49 @@
         <v>16</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="D38" s="2">
-        <v>0.59748427699999995</v>
+        <v>0.86792452799999997</v>
       </c>
       <c r="E38" s="2">
-        <v>0.27857142899999998</v>
+        <v>0.47857142899999999</v>
       </c>
       <c r="F38" s="2">
-        <v>1.9357583000000001E-2</v>
+        <v>0.65241437999999996</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>0.98189819</v>
       </c>
       <c r="H38" s="2">
-        <v>0.42644246600000002</v>
+        <v>0.117479163</v>
       </c>
       <c r="I38" s="2">
-        <v>0.27924324099999998</v>
+        <v>0.24837313</v>
       </c>
       <c r="J38" s="2">
-        <v>0.33333333300000001</v>
+        <v>0</v>
       </c>
       <c r="K38" s="2">
-        <v>0.85792992300000004</v>
+        <v>0.27112415099999998</v>
       </c>
       <c r="L38" s="2">
-        <v>4.957226E-2</v>
+        <v>0.104232407</v>
       </c>
       <c r="M38" s="2">
-        <v>0.81324384800000005</v>
+        <v>0.52805239500000001</v>
       </c>
       <c r="N38" s="2">
-        <v>0.66339290500000003</v>
+        <v>0.71972293200000004</v>
       </c>
       <c r="O38" s="2">
-        <v>0.36603221600000002</v>
+        <v>0.63764200500000001</v>
       </c>
       <c r="P38" s="2">
-        <v>0.35513536200000001</v>
+        <v>0.74866072900000002</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
@@ -6651,49 +6651,49 @@
         <v>16</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D39" s="2">
-        <v>0.78616352199999995</v>
+        <v>0.86163522000000003</v>
       </c>
       <c r="E39" s="2">
-        <v>0.46428571400000002</v>
+        <v>0.59285714300000003</v>
       </c>
       <c r="F39" s="2">
-        <v>0.47202722800000002</v>
+        <v>0.62125079800000005</v>
       </c>
       <c r="G39" s="2">
-        <v>0.89838983900000002</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2">
-        <v>0.17721098699999999</v>
+        <v>0.16151251899999999</v>
       </c>
       <c r="I39" s="2">
-        <v>0.46635305100000002</v>
+        <v>0.25807553700000002</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
       <c r="K39" s="2">
-        <v>0.28716819599999999</v>
+        <v>0.21508503800000001</v>
       </c>
       <c r="L39" s="2">
-        <v>9.1261647000000001E-2</v>
+        <v>0.141206373</v>
       </c>
       <c r="M39" s="2">
-        <v>0.57132369900000002</v>
+        <v>0.58460445400000005</v>
       </c>
       <c r="N39" s="2">
-        <v>1</v>
+        <v>0.93338646800000002</v>
       </c>
       <c r="O39" s="2">
-        <v>0.73689916</v>
+        <v>0.72035622799999999</v>
       </c>
       <c r="P39" s="2">
-        <v>0.69425437300000004</v>
+        <v>0.77767578100000001</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
@@ -6707,49 +6707,49 @@
         <v>16</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D40" s="2">
-        <v>0.71698113200000002</v>
+        <v>0.77358490599999996</v>
       </c>
       <c r="E40" s="2">
-        <v>0.62857142899999996</v>
+        <v>0.571428571</v>
       </c>
       <c r="F40" s="2">
-        <v>0.69336311399999995</v>
+        <v>0.41289087400000002</v>
       </c>
       <c r="G40" s="2">
-        <v>0.87208720900000003</v>
+        <v>0.95229523000000005</v>
       </c>
       <c r="H40" s="2">
-        <v>0.33550995700000003</v>
+        <v>3.0045575000000001E-2</v>
       </c>
       <c r="I40" s="2">
-        <v>0.63325053600000003</v>
+        <v>9.2824107000000003E-2</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
       </c>
       <c r="K40" s="2">
-        <v>0.21098535900000001</v>
+        <v>0.32918704300000001</v>
       </c>
       <c r="L40" s="2">
-        <v>0.22895045</v>
+        <v>0.11259501600000001</v>
       </c>
       <c r="M40" s="2">
-        <v>0.62835392499999998</v>
+        <v>0.57033420099999999</v>
       </c>
       <c r="N40" s="2">
-        <v>0.61310284400000004</v>
+        <v>0.50805836599999998</v>
       </c>
       <c r="O40" s="2">
-        <v>4.4648634E-2</v>
+        <v>0.77854723599999998</v>
       </c>
       <c r="P40" s="2">
-        <v>0.21149828200000001</v>
+        <v>0.80851168699999998</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
@@ -6763,49 +6763,49 @@
         <v>16</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D41" s="2">
-        <v>0.67295597500000004</v>
+        <v>0.84905660400000005</v>
       </c>
       <c r="E41" s="2">
-        <v>0.13571428599999999</v>
+        <v>0.50714285699999995</v>
       </c>
       <c r="F41" s="2">
-        <v>0.17645181900000001</v>
+        <v>0.194320357</v>
       </c>
       <c r="G41" s="2">
-        <v>0.39343934400000002</v>
+        <v>0.96659666</v>
       </c>
       <c r="H41" s="2">
-        <v>0.18398489900000001</v>
+        <v>7.7511843999999996E-2</v>
       </c>
       <c r="I41" s="2">
-        <v>9.1832645000000004E-2</v>
+        <v>0.196932525</v>
       </c>
       <c r="J41" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K41" s="2">
-        <v>0.82139638199999998</v>
+        <v>0.33745886000000003</v>
       </c>
       <c r="L41" s="2">
-        <v>6.2002199000000001E-2</v>
+        <v>7.8070387000000005E-2</v>
       </c>
       <c r="M41" s="2">
-        <v>0.44052065699999998</v>
+        <v>0.48764195799999999</v>
       </c>
       <c r="N41" s="2">
-        <v>0.77337964000000003</v>
+        <v>0.90241119599999997</v>
       </c>
       <c r="O41" s="2">
-        <v>0.485148142</v>
+        <v>0.53012108400000002</v>
       </c>
       <c r="P41" s="2">
-        <v>0.40795188100000002</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
@@ -6819,49 +6819,49 @@
         <v>16</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D42" s="2">
-        <v>0.62893081799999995</v>
+        <v>0.78616352199999995</v>
       </c>
       <c r="E42" s="2">
-        <v>0.8</v>
+        <v>0.46428571400000002</v>
       </c>
       <c r="F42" s="2">
-        <v>0.24686237</v>
+        <v>0.47202722800000002</v>
       </c>
       <c r="G42" s="2">
-        <v>0.70307030699999995</v>
+        <v>0.89838983900000002</v>
       </c>
       <c r="H42" s="2">
-        <v>0.55808644399999996</v>
+        <v>0.17721098699999999</v>
       </c>
       <c r="I42" s="2">
-        <v>1</v>
+        <v>0.46635305100000002</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
       </c>
       <c r="K42" s="2">
-        <v>0.292028063</v>
+        <v>0.28716819599999999</v>
       </c>
       <c r="L42" s="2">
-        <v>0.18962547799999999</v>
+        <v>9.1261647000000001E-2</v>
       </c>
       <c r="M42" s="2">
-        <v>0.705715596</v>
+        <v>0.57132369900000002</v>
       </c>
       <c r="N42" s="2">
-        <v>0.70047848800000001</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2">
-        <v>0.49197468900000002</v>
+        <v>0.73689916</v>
       </c>
       <c r="P42" s="2">
-        <v>0.103590684</v>
+        <v>0.69425437300000004</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
@@ -6875,49 +6875,49 @@
         <v>16</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2">
-        <v>0.75471698099999995</v>
+        <v>0.51572326999999996</v>
       </c>
       <c r="E43" s="2">
-        <v>0.61428571399999998</v>
+        <v>0.59285714300000003</v>
       </c>
       <c r="F43" s="2">
-        <v>0.30344607499999998</v>
+        <v>0.59636247600000003</v>
       </c>
       <c r="G43" s="2">
-        <v>0.88368836900000003</v>
+        <v>0.98899890000000001</v>
       </c>
       <c r="H43" s="2">
-        <v>0.132620195</v>
+        <v>0.183564428</v>
       </c>
       <c r="I43" s="2">
-        <v>0.39791784499999999</v>
+        <v>0.98518585199999997</v>
       </c>
       <c r="J43" s="2">
         <v>0</v>
       </c>
       <c r="K43" s="2">
-        <v>0.25299276500000001</v>
+        <v>0.176834082</v>
       </c>
       <c r="L43" s="2">
-        <v>0.17769315299999999</v>
+        <v>0.274197633</v>
       </c>
       <c r="M43" s="2">
-        <v>0.50065998099999998</v>
+        <v>0.45004276599999998</v>
       </c>
       <c r="N43" s="2">
-        <v>0</v>
+        <v>0.64907111200000001</v>
       </c>
       <c r="O43" s="2">
-        <v>0.65095266399999996</v>
+        <v>0.60666912399999995</v>
       </c>
       <c r="P43" s="2">
-        <v>0.19335734500000001</v>
+        <v>0.73151146700000003</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
@@ -6931,49 +6931,49 @@
         <v>16</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>0.70440251600000003</v>
+        <v>0.56603773599999996</v>
       </c>
       <c r="E44" s="2">
-        <v>0.38571428600000002</v>
+        <v>0.514285714</v>
       </c>
       <c r="F44" s="2">
-        <v>0.100191449</v>
+        <v>0.47415443499999999</v>
       </c>
       <c r="G44" s="2">
-        <v>8.7008700999999994E-2</v>
+        <v>0.92449244900000005</v>
       </c>
       <c r="H44" s="2">
-        <v>0.180815806</v>
+        <v>0.23632636000000001</v>
       </c>
       <c r="I44" s="2">
-        <v>0.23013325900000001</v>
+        <v>0.52037455799999999</v>
       </c>
       <c r="J44" s="2">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2">
-        <v>0.977321467</v>
+        <v>0.304510155</v>
       </c>
       <c r="L44" s="2">
-        <v>9.7733617999999994E-2</v>
+        <v>0.106558085</v>
       </c>
       <c r="M44" s="2">
-        <v>0.57609191199999998</v>
+        <v>0.45292009100000002</v>
       </c>
       <c r="N44" s="2">
-        <v>0.51609956999999995</v>
+        <v>0.75699143800000002</v>
       </c>
       <c r="O44" s="2">
-        <v>0.57591988900000002</v>
+        <v>0.70577476900000002</v>
       </c>
       <c r="P44" s="2">
-        <v>0.45368767300000001</v>
+        <v>0.78043004299999996</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
@@ -6987,49 +6987,49 @@
         <v>16</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D45" s="2">
-        <v>0.371069182</v>
+        <v>0.69182389899999996</v>
       </c>
       <c r="E45" s="2">
-        <v>0.71428571399999996</v>
+        <v>0.39285714300000002</v>
       </c>
       <c r="F45" s="2">
-        <v>0.38672622800000001</v>
+        <v>0.45341416699999998</v>
       </c>
       <c r="G45" s="2">
-        <v>0.97609760999999995</v>
+        <v>0.93179317900000003</v>
       </c>
       <c r="H45" s="2">
-        <v>0.14198671600000001</v>
+        <v>0.21596468199999999</v>
       </c>
       <c r="I45" s="2">
-        <v>0.34739539200000003</v>
+        <v>0.61653771800000001</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
       </c>
       <c r="K45" s="2">
-        <v>0.17040426</v>
+        <v>0.39129240900000001</v>
       </c>
       <c r="L45" s="2">
-        <v>0.25675281100000003</v>
+        <v>8.7891574E-2</v>
       </c>
       <c r="M45" s="2">
-        <v>0.53521248499999996</v>
+        <v>0.40564392900000001</v>
       </c>
       <c r="N45" s="2">
-        <v>0.116742658</v>
+        <v>0.87772592599999999</v>
       </c>
       <c r="O45" s="2">
-        <v>0.62536076500000004</v>
+        <v>0.65187830300000005</v>
       </c>
       <c r="P45" s="2">
-        <v>0.34743216700000001</v>
+        <v>0.88580566699999996</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
@@ -7043,49 +7043,49 @@
         <v>16</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="D46" s="2">
-        <v>0.86163522000000003</v>
+        <v>0.54088050300000001</v>
       </c>
       <c r="E46" s="2">
-        <v>0.59285714300000003</v>
+        <v>0.74285714300000005</v>
       </c>
       <c r="F46" s="2">
-        <v>0.62125079800000005</v>
+        <v>0.41863433300000003</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
       </c>
       <c r="H46" s="2">
-        <v>0.16151251899999999</v>
+        <v>9.8367679E-2</v>
       </c>
       <c r="I46" s="2">
-        <v>0.25807553700000002</v>
+        <v>0.86225275000000001</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
       </c>
       <c r="K46" s="2">
-        <v>0.21508503800000001</v>
+        <v>0.30548390800000003</v>
       </c>
       <c r="L46" s="2">
-        <v>0.141206373</v>
+        <v>0.17419346199999999</v>
       </c>
       <c r="M46" s="2">
-        <v>0.58460445400000005</v>
+        <v>0.42225821200000002</v>
       </c>
       <c r="N46" s="2">
-        <v>0.93338646800000002</v>
+        <v>0.73988199099999996</v>
       </c>
       <c r="O46" s="2">
-        <v>0.72035622799999999</v>
+        <v>0.56049442500000002</v>
       </c>
       <c r="P46" s="2">
-        <v>0.77767578100000001</v>
+        <v>0.72621669600000005</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
@@ -7099,49 +7099,49 @@
         <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D47" s="2">
-        <v>0.76729559700000005</v>
+        <v>0.553459119</v>
       </c>
       <c r="E47" s="2">
-        <v>0.61428571399999998</v>
+        <v>0.821428571</v>
       </c>
       <c r="F47" s="2">
-        <v>0.26632631400000001</v>
+        <v>0.32429270399999999</v>
       </c>
       <c r="G47" s="2">
-        <v>0.33993399299999999</v>
+        <v>0.98799879999999995</v>
       </c>
       <c r="H47" s="2">
-        <v>0.20473272100000001</v>
+        <v>0.30755589799999999</v>
       </c>
       <c r="I47" s="2">
-        <v>0.61361786699999998</v>
+        <v>0.54020447599999999</v>
       </c>
       <c r="J47" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K47" s="2">
-        <v>0.89546137000000003</v>
+        <v>0.281559581</v>
       </c>
       <c r="L47" s="2">
-        <v>1.3027375000000001E-2</v>
+        <v>0.22729968</v>
       </c>
       <c r="M47" s="2">
-        <v>0.78359906000000001</v>
+        <v>0.46549512900000001</v>
       </c>
       <c r="N47" s="2">
-        <v>0.97589071900000002</v>
+        <v>0.51425926600000005</v>
       </c>
       <c r="O47" s="2">
-        <v>0.92274844099999997</v>
+        <v>0.52002510899999999</v>
       </c>
       <c r="P47" s="2">
-        <v>0.41731044099999998</v>
+        <v>0.63646293399999998</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
@@ -7155,49 +7155,49 @@
         <v>16</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D48" s="2">
-        <v>0.80503144699999996</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2">
-        <v>0.34285714299999998</v>
+        <v>0.65714285699999997</v>
       </c>
       <c r="F48" s="2">
-        <v>7.4984045999999999E-2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>0.24532453200000001</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>0.23845611899999999</v>
+        <v>0.242252783</v>
       </c>
       <c r="I48" s="2">
-        <v>0.20531851000000001</v>
+        <v>0.29161058299999998</v>
       </c>
       <c r="J48" s="2">
-        <v>0.16666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2">
-        <v>0.802331923</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>9.4862648999999993E-2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2">
-        <v>0.465835628</v>
+        <v>0.62093195999999995</v>
       </c>
       <c r="N48" s="2">
-        <v>0.33325132099999999</v>
+        <v>0.31168562599999999</v>
       </c>
       <c r="O48" s="2">
-        <v>0.198697084</v>
+        <v>0.213706174</v>
       </c>
       <c r="P48" s="2">
-        <v>0.13909770499999999</v>
+        <v>0.113557749</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
@@ -7267,50 +7267,54 @@
         <v>117</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="D50" s="2">
-        <v>0.23218390799999999</v>
+        <v>0.98620689699999997</v>
       </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="F50" s="2">
+        <v>0.356691429</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0.47270886099999998</v>
+      </c>
       <c r="H50" s="2">
-        <v>1</v>
+        <v>0.27051755900000002</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>0.22012736799999999</v>
       </c>
       <c r="J50" s="2">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="K50" s="2">
-        <v>0.76875000000000004</v>
+        <v>0.11874999999999999</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2">
-        <v>0.17488710499999999</v>
+        <v>0.70778558300000005</v>
       </c>
       <c r="N50" s="2">
-        <v>0.70775835499999995</v>
+        <v>0.46258204400000003</v>
       </c>
       <c r="O50" s="2">
-        <v>0.75587093599999999</v>
+        <v>0.81274622600000002</v>
       </c>
       <c r="P50" s="2">
-        <v>0.61327630499999997</v>
+        <v>0.13037151199999999</v>
       </c>
       <c r="Q50" s="2">
-        <v>0.26358695700000001</v>
+        <v>1</v>
       </c>
       <c r="R50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="2">
-        <v>0.13479623800000001</v>
+        <v>0.77429467100000005</v>
       </c>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
@@ -7321,54 +7325,54 @@
         <v>117</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2">
-        <v>0.15862069000000001</v>
+        <v>0.77701149400000002</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>0.101563366</v>
       </c>
       <c r="G51" s="2">
-        <v>1</v>
+        <v>0.19473417700000001</v>
       </c>
       <c r="H51" s="2">
-        <v>0</v>
+        <v>0.308041273</v>
       </c>
       <c r="I51" s="2">
-        <v>0.55257709499999996</v>
+        <v>0.555278139</v>
       </c>
       <c r="J51" s="2">
         <v>0.125</v>
       </c>
       <c r="K51" s="2">
-        <v>9.5833333000000007E-2</v>
+        <v>0.110416667</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
-        <v>0.37830740899999998</v>
+        <v>0.64315102899999999</v>
       </c>
       <c r="N51" s="2">
-        <v>0</v>
+        <v>0.50884393400000005</v>
       </c>
       <c r="O51" s="2">
-        <v>0</v>
+        <v>0.84994772600000001</v>
       </c>
       <c r="P51" s="2">
-        <v>0.135365561</v>
+        <v>0.31279072800000002</v>
       </c>
       <c r="Q51" s="2">
-        <v>0.93478260899999999</v>
+        <v>0.96195652200000004</v>
       </c>
       <c r="R51" s="2">
-        <v>0.811320755</v>
+        <v>0.72641509400000004</v>
       </c>
       <c r="S51" s="2">
-        <v>0.70689655200000001</v>
+        <v>0.804075235</v>
       </c>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
@@ -7379,52 +7383,52 @@
         <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D52" s="2">
-        <v>0.671264368</v>
+        <v>0.63908045999999996</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2">
-        <v>0.29116310000000001</v>
+        <v>8.0164098000000003E-2</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2">
-        <v>0.42570962200000001</v>
+        <v>0.41451761599999998</v>
       </c>
       <c r="I52" s="2">
-        <v>0.90501119900000004</v>
+        <v>0</v>
       </c>
       <c r="J52" s="2">
-        <v>0.16666666699999999</v>
+        <v>0.375</v>
       </c>
       <c r="K52" s="2">
-        <v>9.5833333000000007E-2</v>
+        <v>0.46875</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
-        <v>0.89434688100000004</v>
+        <v>0.62761331300000001</v>
       </c>
       <c r="N52" s="2">
-        <v>0.35010869100000003</v>
+        <v>0.51800675299999999</v>
       </c>
       <c r="O52" s="2">
-        <v>0.93849121899999999</v>
+        <v>0.71971812800000001</v>
       </c>
       <c r="P52" s="2">
-        <v>1</v>
+        <v>0.76623751500000004</v>
       </c>
       <c r="Q52" s="2">
-        <v>0.72826086999999995</v>
+        <v>0.85597826099999996</v>
       </c>
       <c r="R52" s="2">
-        <v>0.74528301900000005</v>
+        <v>0.52830188700000003</v>
       </c>
       <c r="S52" s="2">
-        <v>0.86833855800000004</v>
+        <v>0.58934169300000006</v>
       </c>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
@@ -7435,52 +7439,52 @@
         <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D53" s="2">
-        <v>0.22758620700000001</v>
+        <v>0.48045977000000001</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2">
-        <v>5.9319215000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2">
-        <v>0.49969216399999999</v>
+        <v>0.63869386500000003</v>
       </c>
       <c r="I53" s="2">
-        <v>0.12765669299999999</v>
+        <v>0.74325503299999995</v>
       </c>
       <c r="J53" s="2">
-        <v>1</v>
+        <v>8.3333332999999996E-2</v>
       </c>
       <c r="K53" s="2">
-        <v>0.38750000000000001</v>
+        <v>0.13125000000000001</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
-        <v>0</v>
+        <v>0.75413948799999997</v>
       </c>
       <c r="N53" s="2">
-        <v>0.98805503800000005</v>
+        <v>0.45364209100000003</v>
       </c>
       <c r="O53" s="2">
-        <v>0.45510288900000001</v>
+        <v>0.95716412699999998</v>
       </c>
       <c r="P53" s="2">
-        <v>0.29169358499999998</v>
+        <v>0.66279626300000005</v>
       </c>
       <c r="Q53" s="2">
-        <v>0.51902173900000004</v>
+        <v>0.38858695700000001</v>
       </c>
       <c r="R53" s="2">
-        <v>0.40566037700000002</v>
+        <v>0.58490565999999999</v>
       </c>
       <c r="S53" s="2">
-        <v>0.76489028199999998</v>
+        <v>1</v>
       </c>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
@@ -7491,52 +7495,52 @@
         <v>117</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D54" s="2">
-        <v>0.222988506</v>
+        <v>0.671264368</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2">
-        <v>1.6964186999999999E-2</v>
+        <v>0.29116310000000001</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2">
-        <v>0.124220229</v>
+        <v>0.42570962200000001</v>
       </c>
       <c r="I54" s="2">
-        <v>0.392087517</v>
+        <v>0.90501119900000004</v>
       </c>
       <c r="J54" s="2">
-        <v>0.58333333300000001</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="K54" s="2">
-        <v>0.32916666700000002</v>
+        <v>9.5833333000000007E-2</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
-        <v>0.49509951499999999</v>
+        <v>0.89434688100000004</v>
       </c>
       <c r="N54" s="2">
-        <v>0.35455024200000002</v>
+        <v>0.35010869100000003</v>
       </c>
       <c r="O54" s="2">
-        <v>0.63528077400000005</v>
+        <v>0.93849121899999999</v>
       </c>
       <c r="P54" s="2">
-        <v>0.67674646900000002</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="2">
-        <v>0.4375</v>
+        <v>0.72826086999999995</v>
       </c>
       <c r="R54" s="2">
-        <v>0.42452830200000002</v>
+        <v>0.74528301900000005</v>
       </c>
       <c r="S54" s="2">
-        <v>0.5</v>
+        <v>0.86833855800000004</v>
       </c>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
@@ -7547,50 +7551,52 @@
         <v>117</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D55" s="2">
-        <v>0.32183908</v>
+        <v>0.92413793099999997</v>
       </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="F55" s="2">
+        <v>0.27309014300000001</v>
+      </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2">
-        <v>0.62466695999999999</v>
+        <v>0.24987319899999999</v>
       </c>
       <c r="I55" s="2">
-        <v>0.48991748200000002</v>
+        <v>0.75646001200000001</v>
       </c>
       <c r="J55" s="2">
-        <v>0.33333333300000001</v>
+        <v>0.125</v>
       </c>
       <c r="K55" s="2">
-        <v>0.32916666700000002</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
-        <v>0.108755645</v>
+        <v>0.62739588599999996</v>
       </c>
       <c r="N55" s="2">
-        <v>1</v>
+        <v>0.42022414299999999</v>
       </c>
       <c r="O55" s="2">
-        <v>0.69388658700000005</v>
+        <v>0.72355444899999999</v>
       </c>
       <c r="P55" s="2">
-        <v>0.38768686600000002</v>
+        <v>0.83485121299999998</v>
       </c>
       <c r="Q55" s="2">
-        <v>0.77717391300000005</v>
+        <v>0.78804347799999996</v>
       </c>
       <c r="R55" s="2">
-        <v>0.35849056600000001</v>
+        <v>0.74528301900000005</v>
       </c>
       <c r="S55" s="2">
-        <v>0.58620689699999995</v>
+        <v>0.91065830699999994</v>
       </c>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -7601,54 +7607,52 @@
         <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D56" s="2">
-        <v>0.48045977000000001</v>
+        <v>0.41839080499999998</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2">
-        <v>7.7503049000000004E-2</v>
-      </c>
-      <c r="G56" s="2">
-        <v>0</v>
-      </c>
+        <v>6.7524115999999995E-2</v>
+      </c>
+      <c r="G56" s="2"/>
       <c r="H56" s="2">
-        <v>0.71737980199999996</v>
+        <v>9.0621864999999996E-2</v>
       </c>
       <c r="I56" s="2">
-        <v>0.31557752100000003</v>
+        <v>0.32505781099999997</v>
       </c>
       <c r="J56" s="2">
-        <v>8.3333332999999996E-2</v>
+        <v>0.45833333300000001</v>
       </c>
       <c r="K56" s="2">
-        <v>0.89583333300000001</v>
+        <v>0.71458333299999999</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
-        <v>0.29602776400000003</v>
+        <v>0.55170597099999996</v>
       </c>
       <c r="N56" s="2">
-        <v>0.55753758899999994</v>
+        <v>0.37802113700000001</v>
       </c>
       <c r="O56" s="2">
-        <v>0.60483021299999995</v>
+        <v>0.62422220900000003</v>
       </c>
       <c r="P56" s="2">
-        <v>0.47077032899999999</v>
+        <v>0.61221555400000005</v>
       </c>
       <c r="Q56" s="2">
-        <v>0.77445652200000004</v>
+        <v>0.44565217400000001</v>
       </c>
       <c r="R56" s="2">
-        <v>0.47169811299999997</v>
+        <v>0.57547169799999998</v>
       </c>
       <c r="S56" s="2">
-        <v>0.18495297799999999</v>
+        <v>0.23824451399999999</v>
       </c>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
@@ -7659,52 +7663,52 @@
         <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D57" s="2">
-        <v>0.14942528699999999</v>
+        <v>0.222988506</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2">
-        <v>0.16509590900000001</v>
+        <v>1.6964186999999999E-2</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2">
-        <v>9.6944058E-2</v>
+        <v>0.124220229</v>
       </c>
       <c r="I57" s="2">
-        <v>0</v>
+        <v>0.392087517</v>
       </c>
       <c r="J57" s="2">
-        <v>0.125</v>
+        <v>0.58333333300000001</v>
       </c>
       <c r="K57" s="2">
-        <v>0.45208333299999998</v>
+        <v>0.32916666700000002</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2">
-        <v>0.30553604299999998</v>
+        <v>0.49509951499999999</v>
       </c>
       <c r="N57" s="2">
-        <v>0.755019408</v>
+        <v>0.35455024200000002</v>
       </c>
       <c r="O57" s="2">
-        <v>0.31797091</v>
+        <v>0.63528077400000005</v>
       </c>
       <c r="P57" s="2">
-        <v>0.14856952800000001</v>
+        <v>0.67674646900000002</v>
       </c>
       <c r="Q57" s="2">
-        <v>0.494565217</v>
+        <v>0.4375</v>
       </c>
       <c r="R57" s="2">
-        <v>0.235849057</v>
+        <v>0.42452830200000002</v>
       </c>
       <c r="S57" s="2">
-        <v>0.57993730399999999</v>
+        <v>0.5</v>
       </c>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
@@ -7715,54 +7719,54 @@
         <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D58" s="2">
-        <v>0.15862069000000001</v>
+        <v>0.48045977000000001</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2">
-        <v>6.9630779000000004E-2</v>
+        <v>7.7503049000000004E-2</v>
       </c>
       <c r="G58" s="2">
-        <v>0.41346835399999998</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2">
-        <v>0.242191566</v>
+        <v>0.71737980199999996</v>
       </c>
       <c r="I58" s="2">
-        <v>1</v>
+        <v>0.31557752100000003</v>
       </c>
       <c r="J58" s="2">
-        <v>0</v>
+        <v>8.3333332999999996E-2</v>
       </c>
       <c r="K58" s="2">
-        <v>0.31041666699999998</v>
+        <v>0.89583333300000001</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
-        <v>0.20341194200000001</v>
+        <v>0.29602776400000003</v>
       </c>
       <c r="N58" s="2">
-        <v>0.69045367599999996</v>
+        <v>0.55753758899999994</v>
       </c>
       <c r="O58" s="2">
-        <v>0.194471751</v>
+        <v>0.60483021299999995</v>
       </c>
       <c r="P58" s="2">
-        <v>0</v>
+        <v>0.47077032899999999</v>
       </c>
       <c r="Q58" s="2">
-        <v>0.94565217400000001</v>
+        <v>0.77445652200000004</v>
       </c>
       <c r="R58" s="2">
-        <v>0.603773585</v>
+        <v>0.47169811299999997</v>
       </c>
       <c r="S58" s="2">
-        <v>0.51880877700000005</v>
+        <v>0.18495297799999999</v>
       </c>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
@@ -7773,41 +7777,55 @@
         <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
+      <c r="F59" s="2">
+        <v>3.2708726E-2</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0.429164557</v>
+      </c>
       <c r="H59" s="2">
-        <v>0.23102926900000001</v>
+        <v>4.2669012999999999E-2</v>
       </c>
       <c r="I59" s="2">
         <v>0</v>
       </c>
       <c r="J59" s="2">
-        <v>0.33333333300000001</v>
-      </c>
-      <c r="K59" s="2"/>
+        <v>0.375</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
-        <v>0.21202542199999999</v>
+        <v>0.38262251200000003</v>
       </c>
       <c r="N59" s="2">
-        <v>0.98106506999999998</v>
+        <v>0.50979775699999996</v>
       </c>
       <c r="O59" s="2">
-        <v>0.35658837300000001</v>
+        <v>0.25529011800000001</v>
       </c>
       <c r="P59" s="2">
-        <v>0.22379164900000001</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
+        <v>0.164281712</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0.15094339600000001</v>
+      </c>
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
@@ -7817,54 +7835,54 @@
         <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D60" s="2">
-        <v>0</v>
+        <v>0.15862069000000001</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2">
-        <v>3.2708726E-2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>0.429164557</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2">
-        <v>4.2669012999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2">
-        <v>0</v>
+        <v>0.55257709499999996</v>
       </c>
       <c r="J60" s="2">
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="K60" s="2">
-        <v>1</v>
+        <v>9.5833333000000007E-2</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2">
-        <v>0.38262251200000003</v>
+        <v>0.37830740899999998</v>
       </c>
       <c r="N60" s="2">
-        <v>0.50979775699999996</v>
+        <v>0</v>
       </c>
       <c r="O60" s="2">
-        <v>0.25529011800000001</v>
+        <v>0</v>
       </c>
       <c r="P60" s="2">
-        <v>0.164281712</v>
+        <v>0.135365561</v>
       </c>
       <c r="Q60" s="2">
-        <v>0</v>
+        <v>0.93478260899999999</v>
       </c>
       <c r="R60" s="2">
-        <v>0.15094339600000001</v>
+        <v>0.811320755</v>
       </c>
       <c r="S60" s="2">
-        <v>0</v>
+        <v>0.70689655200000001</v>
       </c>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
@@ -7875,52 +7893,54 @@
         <v>117</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D61" s="2">
-        <v>0.41839080499999998</v>
+        <v>0.15862069000000001</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2">
-        <v>6.7524115999999995E-2</v>
-      </c>
-      <c r="G61" s="2"/>
+        <v>6.9630779000000004E-2</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0.41346835399999998</v>
+      </c>
       <c r="H61" s="2">
-        <v>9.0621864999999996E-2</v>
+        <v>0.242191566</v>
       </c>
       <c r="I61" s="2">
-        <v>0.32505781099999997</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2">
-        <v>0.45833333300000001</v>
+        <v>0</v>
       </c>
       <c r="K61" s="2">
-        <v>0.71458333299999999</v>
+        <v>0.31041666699999998</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
-        <v>0.55170597099999996</v>
+        <v>0.20341194200000001</v>
       </c>
       <c r="N61" s="2">
-        <v>0.37802113700000001</v>
+        <v>0.69045367599999996</v>
       </c>
       <c r="O61" s="2">
-        <v>0.62422220900000003</v>
+        <v>0.194471751</v>
       </c>
       <c r="P61" s="2">
-        <v>0.61221555400000005</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="2">
-        <v>0.44565217400000001</v>
+        <v>0.94565217400000001</v>
       </c>
       <c r="R61" s="2">
-        <v>0.57547169799999998</v>
+        <v>0.603773585</v>
       </c>
       <c r="S61" s="2">
-        <v>0.23824451399999999</v>
+        <v>0.51880877700000005</v>
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
@@ -7931,52 +7951,52 @@
         <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D62" s="2">
-        <v>0.92413793099999997</v>
+        <v>0.22758620700000001</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2">
-        <v>0.27309014300000001</v>
+        <v>5.9319215000000002E-2</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2">
-        <v>0.24987319899999999</v>
+        <v>0.49969216399999999</v>
       </c>
       <c r="I62" s="2">
-        <v>0.75646001200000001</v>
+        <v>0.12765669299999999</v>
       </c>
       <c r="J62" s="2">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="K62" s="2">
-        <v>5.6250000000000001E-2</v>
+        <v>0.38750000000000001</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
-        <v>0.62739588599999996</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2">
-        <v>0.42022414299999999</v>
+        <v>0.98805503800000005</v>
       </c>
       <c r="O62" s="2">
-        <v>0.72355444899999999</v>
+        <v>0.45510288900000001</v>
       </c>
       <c r="P62" s="2">
-        <v>0.83485121299999998</v>
+        <v>0.29169358499999998</v>
       </c>
       <c r="Q62" s="2">
-        <v>0.78804347799999996</v>
+        <v>0.51902173900000004</v>
       </c>
       <c r="R62" s="2">
-        <v>0.74528301900000005</v>
+        <v>0.40566037700000002</v>
       </c>
       <c r="S62" s="2">
-        <v>0.91065830699999994</v>
+        <v>0.76489028199999998</v>
       </c>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
@@ -7987,52 +8007,50 @@
         <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D63" s="2">
-        <v>0.48045977000000001</v>
+        <v>0.23218390799999999</v>
       </c>
       <c r="E63" s="2"/>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
+      <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2">
-        <v>0.63869386500000003</v>
+        <v>1</v>
       </c>
       <c r="I63" s="2">
-        <v>0.74325503299999995</v>
+        <v>0</v>
       </c>
       <c r="J63" s="2">
-        <v>8.3333332999999996E-2</v>
+        <v>0.25</v>
       </c>
       <c r="K63" s="2">
-        <v>0.13125000000000001</v>
+        <v>0.76875000000000004</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2">
-        <v>0.75413948799999997</v>
+        <v>0.17488710499999999</v>
       </c>
       <c r="N63" s="2">
-        <v>0.45364209100000003</v>
+        <v>0.70775835499999995</v>
       </c>
       <c r="O63" s="2">
-        <v>0.95716412699999998</v>
+        <v>0.75587093599999999</v>
       </c>
       <c r="P63" s="2">
-        <v>0.66279626300000005</v>
+        <v>0.61327630499999997</v>
       </c>
       <c r="Q63" s="2">
-        <v>0.38858695700000001</v>
+        <v>0.26358695700000001</v>
       </c>
       <c r="R63" s="2">
-        <v>0.58490565999999999</v>
+        <v>0</v>
       </c>
       <c r="S63" s="2">
-        <v>1</v>
+        <v>0.13479623800000001</v>
       </c>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
@@ -8043,52 +8061,50 @@
         <v>117</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D64" s="2">
-        <v>0.63908045999999996</v>
+        <v>0.32183908</v>
       </c>
       <c r="E64" s="2"/>
-      <c r="F64" s="2">
-        <v>8.0164098000000003E-2</v>
-      </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2">
-        <v>0.41451761599999998</v>
+        <v>0.62466695999999999</v>
       </c>
       <c r="I64" s="2">
-        <v>0</v>
+        <v>0.48991748200000002</v>
       </c>
       <c r="J64" s="2">
-        <v>0.375</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K64" s="2">
-        <v>0.46875</v>
+        <v>0.32916666700000002</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
-        <v>0.62761331300000001</v>
+        <v>0.108755645</v>
       </c>
       <c r="N64" s="2">
-        <v>0.51800675299999999</v>
+        <v>1</v>
       </c>
       <c r="O64" s="2">
-        <v>0.71971812800000001</v>
+        <v>0.69388658700000005</v>
       </c>
       <c r="P64" s="2">
-        <v>0.76623751500000004</v>
+        <v>0.38768686600000002</v>
       </c>
       <c r="Q64" s="2">
-        <v>0.85597826099999996</v>
+        <v>0.77717391300000005</v>
       </c>
       <c r="R64" s="2">
-        <v>0.52830188700000003</v>
+        <v>0.35849056600000001</v>
       </c>
       <c r="S64" s="2">
-        <v>0.58934169300000006</v>
+        <v>0.58620689699999995</v>
       </c>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
@@ -8099,55 +8115,41 @@
         <v>117</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0.77701149400000002</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2">
-        <v>0.101563366</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0.19473417700000001</v>
-      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="2">
-        <v>0.308041273</v>
+        <v>0.23102926900000001</v>
       </c>
       <c r="I65" s="2">
-        <v>0.555278139</v>
+        <v>0</v>
       </c>
       <c r="J65" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="K65" s="2">
-        <v>0.110416667</v>
-      </c>
+        <v>0.33333333300000001</v>
+      </c>
+      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
-        <v>0.64315102899999999</v>
+        <v>0.21202542199999999</v>
       </c>
       <c r="N65" s="2">
-        <v>0.50884393400000005</v>
+        <v>0.98106506999999998</v>
       </c>
       <c r="O65" s="2">
-        <v>0.84994772600000001</v>
+        <v>0.35658837300000001</v>
       </c>
       <c r="P65" s="2">
-        <v>0.31279072800000002</v>
-      </c>
-      <c r="Q65" s="2">
-        <v>0.96195652200000004</v>
-      </c>
-      <c r="R65" s="2">
-        <v>0.72641509400000004</v>
-      </c>
-      <c r="S65" s="2">
-        <v>0.804075235</v>
-      </c>
+        <v>0.22379164900000001</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
@@ -8157,54 +8159,52 @@
         <v>117</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D66" s="2">
-        <v>0.98620689699999997</v>
+        <v>0.14942528699999999</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2">
-        <v>0.356691429</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0.47270886099999998</v>
-      </c>
+        <v>0.16509590900000001</v>
+      </c>
+      <c r="G66" s="2"/>
       <c r="H66" s="2">
-        <v>0.27051755900000002</v>
+        <v>9.6944058E-2</v>
       </c>
       <c r="I66" s="2">
-        <v>0.22012736799999999</v>
+        <v>0</v>
       </c>
       <c r="J66" s="2">
         <v>0.125</v>
       </c>
       <c r="K66" s="2">
-        <v>0.11874999999999999</v>
+        <v>0.45208333299999998</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2">
-        <v>0.70778558300000005</v>
+        <v>0.30553604299999998</v>
       </c>
       <c r="N66" s="2">
-        <v>0.46258204400000003</v>
+        <v>0.755019408</v>
       </c>
       <c r="O66" s="2">
-        <v>0.81274622600000002</v>
+        <v>0.31797091</v>
       </c>
       <c r="P66" s="2">
-        <v>0.13037151199999999</v>
+        <v>0.14856952800000001</v>
       </c>
       <c r="Q66" s="2">
-        <v>1</v>
+        <v>0.494565217</v>
       </c>
       <c r="R66" s="2">
-        <v>1</v>
+        <v>0.235849057</v>
       </c>
       <c r="S66" s="2">
-        <v>0.77429467100000005</v>
+        <v>0.57993730399999999</v>
       </c>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
@@ -8771,6 +8771,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V76">
+    <sortCondition ref="B1:B76"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
